--- a/contagion/160216_Bankscope.xlsx
+++ b/contagion/160216_Bankscope.xlsx
@@ -6692,7 +6692,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
